--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47328927-B3A7-47F1-945E-2DB141A98F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6D51D3-CDE8-4A44-9508-DD80768968A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="18">
   <si>
     <t>CONTROLE DE GASTOS</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>CUSTO POR PONTO CONCLUÍDO</t>
+  </si>
+  <si>
+    <t>VIAGEM 04</t>
   </si>
 </sst>
 </file>
@@ -541,21 +544,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="5" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="4" max="4" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="5" customWidth="1"/>
+    <col min="6" max="6" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="5" customWidth="1"/>
+    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="5" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -567,8 +572,10 @@
       <c r="G1" s="17"/>
       <c r="H1" s="17"/>
       <c r="I1" s="17"/>
-    </row>
-    <row r="2" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+    </row>
+    <row r="2" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -594,10 +601,16 @@
         <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -622,12 +635,18 @@
       <c r="H3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="5">
-        <f t="shared" ref="I3:I10" si="0">C3+E3+G3</f>
+      <c r="I3" s="4">
+        <v>445.05</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <f t="shared" ref="K3:K10" si="0">C3+E3+G3</f>
         <v>6219.34</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -652,12 +671,18 @@
       <c r="H4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
+        <v>38</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" s="9">
         <f t="shared" si="0"/>
         <v>3430.2599999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -682,12 +707,18 @@
       <c r="H5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
         <f t="shared" si="0"/>
         <v>355.84</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -712,12 +743,18 @@
       <c r="H6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
+        <v>48</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="9">
         <f t="shared" si="0"/>
         <v>592.93000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -742,12 +779,18 @@
       <c r="H7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5">
         <f t="shared" si="0"/>
         <v>3897.79</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
@@ -768,12 +811,18 @@
       <c r="H8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
+        <v>600</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K8" s="9">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>6</v>
       </c>
@@ -798,15 +847,20 @@
         <f>SUM(G3:G8)</f>
         <v>5996.16</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>2</v>
-      </c>
+      <c r="H9" s="11"/>
       <c r="I9" s="11">
-        <f t="shared" si="0"/>
-        <v>15096.16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f>SUM(I3:I8)</f>
+        <v>1131.05</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="11">
+        <f>C9+E9+G9+I9</f>
+        <v>16227.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>13</v>
       </c>
@@ -824,11 +878,14 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>14</v>
       </c>
@@ -853,12 +910,14 @@
         <f>IF(G10&gt;0,G9/G10,0)</f>
         <v>399.74399999999997</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>6</v>
       </c>
@@ -869,12 +928,14 @@
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
-      <c r="I14" s="14">
-        <f>I9</f>
-        <v>15096.16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="14">
+        <f>K9</f>
+        <v>16227.21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>15</v>
       </c>
@@ -885,12 +946,14 @@
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
-      <c r="I15" s="15">
-        <f>I10</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="15">
+        <f>K10</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>16</v>
       </c>
@@ -901,14 +964,16 @@
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
-      <c r="I16" s="14">
-        <f>I14/I15</f>
-        <v>431.31885714285715</v>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="14">
+        <f>K14/K15</f>
+        <v>324.54419999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6D51D3-CDE8-4A44-9508-DD80768968A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DA8309-B630-43A8-9796-E69E11779E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -630,7 +630,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="4">
-        <v>2081.9700000000003</v>
+        <v>2039.46</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>2</v>
@@ -642,8 +642,8 @@
         <v>2</v>
       </c>
       <c r="K3" s="5">
-        <f t="shared" ref="K3:K10" si="0">C3+E3+G3</f>
-        <v>6219.34</v>
+        <f t="shared" ref="K3:K8" si="0">C3+E3+G3</f>
+        <v>6176.83</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -666,20 +666,20 @@
         <v>2</v>
       </c>
       <c r="G4" s="8">
-        <v>1221.6799999999998</v>
+        <v>1267.8599999999999</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="I4" s="8">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="9">
         <f t="shared" si="0"/>
-        <v>3430.2599999999998</v>
+        <v>3476.4399999999996</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -702,7 +702,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="4">
-        <v>160.57999999999998</v>
+        <v>189.26</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>2</v>
@@ -715,7 +715,7 @@
       </c>
       <c r="K5" s="5">
         <f t="shared" si="0"/>
-        <v>355.84</v>
+        <v>384.52</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -738,7 +738,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="8">
-        <v>200.93</v>
+        <v>168.58</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>2</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="K6" s="9">
         <f t="shared" si="0"/>
-        <v>592.93000000000006</v>
+        <v>560.58000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -850,14 +850,14 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11">
         <f>SUM(I3:I8)</f>
-        <v>1131.05</v>
+        <v>1176.05</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>2</v>
       </c>
       <c r="K9" s="11">
         <f>C9+E9+G9+I9</f>
-        <v>16227.21</v>
+        <v>16272.21</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -932,7 +932,7 @@
       <c r="J14" s="12"/>
       <c r="K14" s="14">
         <f>K9</f>
-        <v>16227.21</v>
+        <v>16272.21</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -968,7 +968,7 @@
       <c r="J16" s="12"/>
       <c r="K16" s="14">
         <f>K14/K15</f>
-        <v>324.54419999999999</v>
+        <v>325.44419999999997</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DA8309-B630-43A8-9796-E69E11779E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6590AA7C-8201-41ED-AF84-354D9DB75E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -636,7 +636,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>445.05</v>
+        <v>961.09</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>2</v>
@@ -672,7 +672,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="8">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>2</v>
@@ -744,7 +744,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="8">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>2</v>
@@ -780,7 +780,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="4">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>2</v>
@@ -850,14 +850,14 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11">
         <f>SUM(I3:I8)</f>
-        <v>1176.05</v>
+        <v>2024.0900000000001</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>2</v>
       </c>
       <c r="K9" s="11">
         <f>C9+E9+G9+I9</f>
-        <v>16272.21</v>
+        <v>17120.25</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -932,7 +932,7 @@
       <c r="J14" s="12"/>
       <c r="K14" s="14">
         <f>K9</f>
-        <v>16272.21</v>
+        <v>17120.25</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -968,7 +968,7 @@
       <c r="J16" s="12"/>
       <c r="K16" s="14">
         <f>K14/K15</f>
-        <v>325.44419999999997</v>
+        <v>342.40499999999997</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6590AA7C-8201-41ED-AF84-354D9DB75E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5234B3-9FB0-4A83-BA3D-D206E123270D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -215,9 +215,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -561,19 +558,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
     </row>
     <row r="2" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -636,14 +633,14 @@
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>961.09</v>
+        <v>1347.35</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K3" s="5">
-        <f t="shared" ref="K3:K8" si="0">C3+E3+G3</f>
-        <v>6176.83</v>
+        <f>C3+E3+G3+I3</f>
+        <v>7524.18</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -672,14 +669,14 @@
         <v>2</v>
       </c>
       <c r="I4" s="8">
-        <v>175</v>
+        <v>289</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="9">
-        <f t="shared" si="0"/>
-        <v>3476.4399999999996</v>
+      <c r="K4" s="5">
+        <f t="shared" ref="K4:K8" si="0">C4+E4+G4+I4</f>
+        <v>3765.4399999999996</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -708,14 +705,14 @@
         <v>2</v>
       </c>
       <c r="I5" s="4">
-        <v>0</v>
+        <v>51.34</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K5" s="5">
         <f t="shared" si="0"/>
-        <v>384.52</v>
+        <v>435.86</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -749,9 +746,9 @@
       <c r="J6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="5">
         <f t="shared" si="0"/>
-        <v>560.58000000000004</v>
+        <v>618.58000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -780,14 +777,14 @@
         <v>2</v>
       </c>
       <c r="I7" s="4">
-        <v>230</v>
+        <v>480</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K7" s="5">
         <f t="shared" si="0"/>
-        <v>3897.79</v>
+        <v>4377.79</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -817,51 +814,51 @@
       <c r="J8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="5">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="11">
+      <c r="B9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="10">
         <f>SUM(C3:C8)</f>
         <v>5900</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="11">
+      <c r="D9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="10">
         <f>SUM(E3:E8)</f>
         <v>3200</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="F9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="10">
         <f>SUM(G3:G8)</f>
         <v>5996.16</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11">
+      <c r="H9" s="10"/>
+      <c r="I9" s="10">
         <f>SUM(I3:I8)</f>
-        <v>2024.0900000000001</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="K9" s="11">
+        <v>2825.6899999999996</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="10">
         <f>C9+E9+G9+I9</f>
-        <v>17120.25</v>
+        <v>17921.849999999999</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="1"/>
@@ -886,89 +883,89 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="13">
+      <c r="B11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="12">
         <f>IF(C10&gt;0,C9/C10,0)</f>
         <v>393.33333333333331</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="13">
+      <c r="D11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="12">
         <f>IF(E10&gt;0,E9/E10,0)</f>
         <v>640</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="13">
+      <c r="F11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="12">
         <f>IF(G10&gt;0,G9/G10,0)</f>
         <v>399.74399999999997</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="14">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="13">
         <f>K9</f>
-        <v>17120.25</v>
+        <v>17921.849999999999</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="15">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="14">
         <f>K10</f>
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="14">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="13">
         <f>K14/K15</f>
-        <v>342.40499999999997</v>
+        <v>358.43699999999995</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5234B3-9FB0-4A83-BA3D-D206E123270D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F29E52E-976D-41AB-A346-C79968C95A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -669,14 +669,14 @@
         <v>2</v>
       </c>
       <c r="I4" s="8">
-        <v>289</v>
+        <v>438.78</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="5">
         <f t="shared" ref="K4:K8" si="0">C4+E4+G4+I4</f>
-        <v>3765.4399999999996</v>
+        <v>3915.2199999999993</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -705,14 +705,14 @@
         <v>2</v>
       </c>
       <c r="I5" s="4">
-        <v>51.34</v>
+        <v>58.52</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K5" s="5">
         <f t="shared" si="0"/>
-        <v>435.86</v>
+        <v>443.03999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -741,14 +741,14 @@
         <v>2</v>
       </c>
       <c r="I6" s="8">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K6" s="5">
         <f t="shared" si="0"/>
-        <v>618.58000000000004</v>
+        <v>635.58000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -777,14 +777,14 @@
         <v>2</v>
       </c>
       <c r="I7" s="4">
-        <v>480</v>
+        <v>750</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K7" s="5">
         <f t="shared" si="0"/>
-        <v>4377.79</v>
+        <v>4647.79</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -847,14 +847,14 @@
       <c r="H9" s="10"/>
       <c r="I9" s="10">
         <f>SUM(I3:I8)</f>
-        <v>2825.6899999999996</v>
+        <v>3269.6499999999996</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="K9" s="10">
         <f>C9+E9+G9+I9</f>
-        <v>17921.849999999999</v>
+        <v>18365.809999999998</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -929,7 +929,7 @@
       <c r="J14" s="11"/>
       <c r="K14" s="13">
         <f>K9</f>
-        <v>17921.849999999999</v>
+        <v>18365.809999999998</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -965,7 +965,7 @@
       <c r="J16" s="11"/>
       <c r="K16" s="13">
         <f>K14/K15</f>
-        <v>358.43699999999995</v>
+        <v>367.31619999999998</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F29E52E-976D-41AB-A346-C79968C95A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA3AAA7-5BE6-4206-B757-E8D8A26A39D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -633,14 +633,14 @@
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>1347.35</v>
+        <v>2347.1</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K3" s="5">
         <f>C3+E3+G3+I3</f>
-        <v>7524.18</v>
+        <v>8523.93</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -669,14 +669,14 @@
         <v>2</v>
       </c>
       <c r="I4" s="8">
-        <v>438.78</v>
+        <v>1128.44</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="5">
         <f t="shared" ref="K4:K8" si="0">C4+E4+G4+I4</f>
-        <v>3915.2199999999993</v>
+        <v>4604.8799999999992</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -705,14 +705,14 @@
         <v>2</v>
       </c>
       <c r="I5" s="4">
-        <v>58.52</v>
+        <v>181.87</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K5" s="5">
         <f t="shared" si="0"/>
-        <v>443.03999999999996</v>
+        <v>566.39</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -741,14 +741,14 @@
         <v>2</v>
       </c>
       <c r="I6" s="8">
-        <v>75</v>
+        <v>81.5</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K6" s="5">
         <f t="shared" si="0"/>
-        <v>635.58000000000004</v>
+        <v>642.08000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -777,14 +777,14 @@
         <v>2</v>
       </c>
       <c r="I7" s="4">
-        <v>750</v>
+        <v>1530</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K7" s="5">
         <f t="shared" si="0"/>
-        <v>4647.79</v>
+        <v>5427.79</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -847,14 +847,14 @@
       <c r="H9" s="10"/>
       <c r="I9" s="10">
         <f>SUM(I3:I8)</f>
-        <v>3269.6499999999996</v>
+        <v>5868.91</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="K9" s="10">
         <f>C9+E9+G9+I9</f>
-        <v>18365.809999999998</v>
+        <v>20965.07</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -929,7 +929,7 @@
       <c r="J14" s="11"/>
       <c r="K14" s="13">
         <f>K9</f>
-        <v>18365.809999999998</v>
+        <v>20965.07</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -965,7 +965,7 @@
       <c r="J16" s="11"/>
       <c r="K16" s="13">
         <f>K14/K15</f>
-        <v>367.31619999999998</v>
+        <v>419.3014</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA3AAA7-5BE6-4206-B757-E8D8A26A39D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B24A350-19FA-40CA-A1D2-33647E8D266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -633,14 +633,14 @@
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>2347.1</v>
+        <v>2797.1</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="K3" s="5">
         <f>C3+E3+G3+I3</f>
-        <v>8523.93</v>
+        <v>8973.93</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -669,14 +669,14 @@
         <v>2</v>
       </c>
       <c r="I4" s="8">
-        <v>1128.44</v>
+        <v>1188.44</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="5">
         <f t="shared" ref="K4:K8" si="0">C4+E4+G4+I4</f>
-        <v>4604.8799999999992</v>
+        <v>4664.8799999999992</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -741,14 +741,14 @@
         <v>2</v>
       </c>
       <c r="I6" s="8">
-        <v>81.5</v>
+        <v>425.13</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K6" s="5">
         <f t="shared" si="0"/>
-        <v>642.08000000000004</v>
+        <v>985.71</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -847,14 +847,14 @@
       <c r="H9" s="10"/>
       <c r="I9" s="10">
         <f>SUM(I3:I8)</f>
-        <v>5868.91</v>
+        <v>6722.54</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="K9" s="10">
         <f>C9+E9+G9+I9</f>
-        <v>20965.07</v>
+        <v>21818.7</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -929,7 +929,7 @@
       <c r="J14" s="11"/>
       <c r="K14" s="13">
         <f>K9</f>
-        <v>20965.07</v>
+        <v>21818.7</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -965,7 +965,7 @@
       <c r="J16" s="11"/>
       <c r="K16" s="13">
         <f>K14/K15</f>
-        <v>419.3014</v>
+        <v>436.37400000000002</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B24A350-19FA-40CA-A1D2-33647E8D266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB5EB5F-893D-4769-9442-0F0FA0FB9A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="19">
   <si>
     <t>CONTROLE DE GASTOS</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>VIAGEM 04</t>
+  </si>
+  <si>
+    <t>VIAGEM 05</t>
   </si>
 </sst>
 </file>
@@ -541,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -553,11 +556,13 @@
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="5" customWidth="1"/>
+    <col min="10" max="10" width="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="5" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -571,8 +576,10 @@
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="16"/>
-    </row>
-    <row r="2" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+    </row>
+    <row r="2" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -604,10 +611,16 @@
         <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -638,12 +651,18 @@
       <c r="J3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="4">
+        <v>389.67</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
         <f>C3+E3+G3+I3</f>
         <v>8973.93</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -674,12 +693,18 @@
       <c r="J4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="5">
-        <f t="shared" ref="K4:K8" si="0">C4+E4+G4+I4</f>
+      <c r="K4" s="8">
+        <v>45</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <f t="shared" ref="M4:M8" si="0">C4+E4+G4+I4</f>
         <v>4664.8799999999992</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -710,12 +735,18 @@
       <c r="J5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
+        <v>25.8</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
         <f t="shared" si="0"/>
         <v>566.39</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -746,12 +777,18 @@
       <c r="J6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="8">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
         <f t="shared" si="0"/>
         <v>985.71</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -782,23 +819,33 @@
       <c r="J7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M7" s="5">
         <f t="shared" si="0"/>
         <v>5427.79</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="8"/>
+      <c r="C8" s="8">
+        <v>0</v>
+      </c>
       <c r="D8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
       <c r="F8" s="7" t="s">
         <v>2</v>
       </c>
@@ -814,12 +861,18 @@
       <c r="J8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="8">
+        <v>600</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M8" s="5">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
@@ -849,15 +902,20 @@
         <f>SUM(I3:I8)</f>
         <v>6722.54</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>2</v>
-      </c>
+      <c r="J9" s="10"/>
       <c r="K9" s="10">
-        <f>C9+E9+G9+I9</f>
-        <v>21818.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f>SUM(K3:K8)</f>
+        <v>1060.47</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="M9" s="10">
+        <f>C9+E9+G9+I9+K9</f>
+        <v>22879.170000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -878,11 +936,14 @@
         <v>15</v>
       </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="1">
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1">
+        <f>C10+E10+G10+I10+K10</f>
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -908,13 +969,21 @@
         <v>399.74399999999997</v>
       </c>
       <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I11" s="12">
+        <f>IF(I10&gt;0,I9/I10,0)</f>
+        <v>448.16933333333333</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="12">
+        <f>IF(M10&gt;0,M9/M10,0)</f>
+        <v>457.58340000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>6</v>
       </c>
@@ -927,12 +996,14 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
-      <c r="K14" s="13">
-        <f>K9</f>
-        <v>21818.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="13">
+        <f>M9</f>
+        <v>22879.170000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>15</v>
       </c>
@@ -945,12 +1016,14 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
-      <c r="K15" s="14">
-        <f>K10</f>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="14">
+        <f>M10</f>
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
@@ -963,14 +1036,16 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
-      <c r="K16" s="13">
-        <f>K14/K15</f>
-        <v>436.37400000000002</v>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="13">
+        <f>M14/M15</f>
+        <v>457.58340000000004</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB5EB5F-893D-4769-9442-0F0FA0FB9A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36D1AFD-3A8E-487A-BA12-E59D6B2549E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -652,7 +652,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="4">
-        <v>389.67</v>
+        <v>736.28</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>2</v>
@@ -694,7 +694,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="8">
-        <v>45</v>
+        <v>347.17</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>2</v>
@@ -736,7 +736,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="4">
-        <v>25.8</v>
+        <v>56.9</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>2</v>
@@ -778,7 +778,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8">
-        <v>0</v>
+        <v>161.44</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>2</v>
@@ -820,7 +820,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="4">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>2</v>
@@ -905,14 +905,14 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10">
         <f>SUM(K3:K8)</f>
-        <v>1060.47</v>
+        <v>2301.79</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="M9" s="10">
         <f>C9+E9+G9+I9+K9</f>
-        <v>22879.170000000002</v>
+        <v>24120.49</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -936,11 +936,13 @@
         <v>15</v>
       </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1">
+        <v>15</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1">
         <f>C10+E10+G10+I10+K10</f>
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -978,7 +980,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>457.58340000000004</v>
+        <v>371.08446153846154</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1000,7 +1002,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="13">
         <f>M9</f>
-        <v>22879.170000000002</v>
+        <v>24120.49</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1020,7 +1022,7 @@
       <c r="L15" s="11"/>
       <c r="M15" s="14">
         <f>M10</f>
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1040,7 +1042,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="13">
         <f>M14/M15</f>
-        <v>457.58340000000004</v>
+        <v>371.08446153846154</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36D1AFD-3A8E-487A-BA12-E59D6B2549E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F421D9E6-1CCC-4EAC-A16B-D7BFF47F17C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -652,7 +652,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="4">
-        <v>736.28</v>
+        <v>1186.33</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>2</v>
@@ -694,7 +694,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="8">
-        <v>347.17</v>
+        <v>668.78</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>2</v>
@@ -736,7 +736,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="4">
-        <v>56.9</v>
+        <v>115.53</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>2</v>
@@ -778,7 +778,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8">
-        <v>161.44</v>
+        <v>360.65</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>2</v>
@@ -820,7 +820,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="4">
-        <v>400</v>
+        <v>860</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>2</v>
@@ -905,14 +905,14 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10">
         <f>SUM(K3:K8)</f>
-        <v>2301.79</v>
+        <v>3791.29</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="M9" s="10">
         <f>C9+E9+G9+I9+K9</f>
-        <v>24120.49</v>
+        <v>25609.99</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>371.08446153846154</v>
+        <v>393.99984615384619</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1002,7 +1002,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="13">
         <f>M9</f>
-        <v>24120.49</v>
+        <v>25609.99</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1042,7 +1042,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="13">
         <f>M14/M15</f>
-        <v>371.08446153846154</v>
+        <v>393.99984615384619</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F421D9E6-1CCC-4EAC-A16B-D7BFF47F17C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E41AFC-E9B3-4CDE-B5FB-F43AF89AC800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -652,7 +652,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="4">
-        <v>1186.33</v>
+        <v>2080.4899999999998</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>2</v>
@@ -694,7 +694,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="8">
-        <v>668.78</v>
+        <v>1088.26</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>2</v>
@@ -736,7 +736,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="4">
-        <v>115.53</v>
+        <v>203.26</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>2</v>
@@ -778,7 +778,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8">
-        <v>360.65</v>
+        <v>371.45</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>2</v>
@@ -820,7 +820,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="4">
-        <v>860</v>
+        <v>1430</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>2</v>
@@ -905,14 +905,14 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10">
         <f>SUM(K3:K8)</f>
-        <v>3791.29</v>
+        <v>5773.46</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="M9" s="10">
         <f>C9+E9+G9+I9+K9</f>
-        <v>25609.99</v>
+        <v>27592.16</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>393.99984615384619</v>
+        <v>424.49476923076924</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1002,7 +1002,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="13">
         <f>M9</f>
-        <v>25609.99</v>
+        <v>27592.16</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1042,7 +1042,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="13">
         <f>M14/M15</f>
-        <v>393.99984615384619</v>
+        <v>424.49476923076924</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E41AFC-E9B3-4CDE-B5FB-F43AF89AC800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBDF2BD-1E1F-4EA3-94A1-E0DF3FDD93D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -694,7 +694,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="8">
-        <v>1088.26</v>
+        <v>1203.76</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>2</v>
@@ -736,7 +736,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="4">
-        <v>203.26</v>
+        <v>230.06</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>2</v>
@@ -905,14 +905,14 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10">
         <f>SUM(K3:K8)</f>
-        <v>5773.46</v>
+        <v>5915.76</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="M9" s="10">
         <f>C9+E9+G9+I9+K9</f>
-        <v>27592.16</v>
+        <v>27734.46</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>424.49476923076924</v>
+        <v>426.68399999999997</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1002,7 +1002,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="13">
         <f>M9</f>
-        <v>27592.16</v>
+        <v>27734.46</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1042,7 +1042,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="13">
         <f>M14/M15</f>
-        <v>424.49476923076924</v>
+        <v>426.68399999999997</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBDF2BD-1E1F-4EA3-94A1-E0DF3FDD93D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8406D7-A6BE-4258-91C4-89556093CB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -820,7 +820,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="4">
-        <v>1430</v>
+        <v>1930</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>2</v>
@@ -905,14 +905,14 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10">
         <f>SUM(K3:K8)</f>
-        <v>5915.76</v>
+        <v>6415.76</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="M9" s="10">
         <f>C9+E9+G9+I9+K9</f>
-        <v>27734.46</v>
+        <v>28234.46</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>426.68399999999997</v>
+        <v>434.37630769230771</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1002,7 +1002,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="13">
         <f>M9</f>
-        <v>27734.46</v>
+        <v>28234.46</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1042,7 +1042,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="13">
         <f>M14/M15</f>
-        <v>426.68399999999997</v>
+        <v>434.37630769230771</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8406D7-A6BE-4258-91C4-89556093CB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BCE1D3-21BC-4651-BDC9-503B827EE4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -778,7 +778,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8">
-        <v>371.45</v>
+        <v>431.45</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>2</v>
@@ -905,14 +905,14 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10">
         <f>SUM(K3:K8)</f>
-        <v>6415.76</v>
+        <v>6475.76</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="M9" s="10">
         <f>C9+E9+G9+I9+K9</f>
-        <v>28234.46</v>
+        <v>28294.46</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>434.37630769230771</v>
+        <v>435.29938461538461</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1002,7 +1002,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="13">
         <f>M9</f>
-        <v>28234.46</v>
+        <v>28294.46</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1042,7 +1042,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="13">
         <f>M14/M15</f>
-        <v>434.37630769230771</v>
+        <v>435.29938461538461</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BCE1D3-21BC-4651-BDC9-503B827EE4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2700B070-FB93-4D26-9A44-9EAAFD6A9B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="20">
   <si>
     <t>CONTROLE DE GASTOS</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>VIAGEM 05</t>
+  </si>
+  <si>
+    <t>VIAGEM 06</t>
   </si>
 </sst>
 </file>
@@ -544,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -558,11 +561,13 @@
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="5" customWidth="1"/>
+    <col min="12" max="12" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="5" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -578,8 +583,10 @@
       <c r="K1" s="16"/>
       <c r="L1" s="16"/>
       <c r="M1" s="16"/>
-    </row>
-    <row r="2" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+    </row>
+    <row r="2" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -617,10 +624,16 @@
         <v>2</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -657,12 +670,18 @@
       <c r="L3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="4">
+        <v>365.02</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="5">
         <f>C3+E3+G3+I3</f>
         <v>8973.93</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -699,12 +718,18 @@
       <c r="L4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="5">
-        <f t="shared" ref="M4:M8" si="0">C4+E4+G4+I4</f>
+      <c r="M4" s="8">
+        <v>70.2</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="O4" s="5">
+        <f t="shared" ref="O4:O8" si="0">C4+E4+G4+I4</f>
         <v>4664.8799999999992</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -741,12 +766,18 @@
       <c r="L5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O5" s="5">
         <f t="shared" si="0"/>
         <v>566.39</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -783,12 +814,18 @@
       <c r="L6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="8">
+        <v>1292.5</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6" s="5">
         <f t="shared" si="0"/>
         <v>985.71</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -825,12 +862,18 @@
       <c r="L7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O7" s="5">
         <f t="shared" si="0"/>
         <v>5427.79</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
@@ -867,12 +910,18 @@
       <c r="L8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="8">
+        <v>600</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="O8" s="5">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
@@ -897,12 +946,16 @@
         <f>SUM(G3:G8)</f>
         <v>5996.16</v>
       </c>
-      <c r="H9" s="10"/>
+      <c r="H9" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="I9" s="10">
         <f>SUM(I3:I8)</f>
         <v>6722.54</v>
       </c>
-      <c r="J9" s="10"/>
+      <c r="J9" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="K9" s="10">
         <f>SUM(K3:K8)</f>
         <v>6475.76</v>
@@ -911,11 +964,18 @@
         <v>2</v>
       </c>
       <c r="M9" s="10">
-        <f>C9+E9+G9+I9+K9</f>
-        <v>28294.46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f>SUM(M3:M8)</f>
+        <v>2327.7200000000003</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="O9" s="10">
+        <f>C9+E9+G9+I9+K9+M9</f>
+        <v>30622.18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -941,11 +1001,15 @@
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1">
-        <f>C10+E10+G10+I10+K10</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1">
+        <f>C10+E10+G10+I10+K10+M10</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -976,16 +1040,24 @@
         <v>448.16933333333333</v>
       </c>
       <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="1"/>
+      <c r="K11" s="12">
+        <f>IF(K10&gt;0,K9/K10,0)</f>
+        <v>431.71733333333333</v>
+      </c>
+      <c r="L11" s="12"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>435.29938461538461</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>155.18133333333336</v>
+      </c>
+      <c r="N11" s="1"/>
+      <c r="O11" s="12">
+        <f>IF(O10&gt;0,O9/O10,0)</f>
+        <v>382.77724999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>6</v>
       </c>
@@ -1000,12 +1072,14 @@
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
-      <c r="M14" s="13">
-        <f>M9</f>
-        <v>28294.46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="13">
+        <f>O9</f>
+        <v>30622.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>15</v>
       </c>
@@ -1020,12 +1094,14 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
-      <c r="M15" s="14">
-        <f>M10</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="14">
+        <f>O10</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
@@ -1040,14 +1116,16 @@
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
-      <c r="M16" s="13">
-        <f>M14/M15</f>
-        <v>435.29938461538461</v>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="13">
+        <f>O14/O15</f>
+        <v>382.77724999999998</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2700B070-FB93-4D26-9A44-9EAAFD6A9B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC5B181-83C8-49B9-9189-1B09C09C88D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,7 +671,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="4">
-        <v>365.02</v>
+        <v>785.31</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>2</v>
@@ -719,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="M4" s="8">
-        <v>70.2</v>
+        <v>226.2</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>2</v>
@@ -767,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="M5" s="4">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>2</v>
@@ -965,14 +965,14 @@
       </c>
       <c r="M9" s="10">
         <f>SUM(M3:M8)</f>
-        <v>2327.7200000000003</v>
+        <v>2926.81</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="O9" s="10">
         <f>C9+E9+G9+I9+K9+M9</f>
-        <v>30622.18</v>
+        <v>31221.27</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1047,12 +1047,12 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>155.18133333333336</v>
+        <v>195.12066666666666</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
-        <v>382.77724999999998</v>
+        <v>390.26587499999999</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1076,7 +1076,7 @@
       <c r="N14" s="11"/>
       <c r="O14" s="13">
         <f>O9</f>
-        <v>30622.18</v>
+        <v>31221.27</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       <c r="N16" s="11"/>
       <c r="O16" s="13">
         <f>O14/O15</f>
-        <v>382.77724999999998</v>
+        <v>390.26587499999999</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC5B181-83C8-49B9-9189-1B09C09C88D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC42215-2C42-497A-B1AD-FABB5592682A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,7 +671,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="4">
-        <v>785.31</v>
+        <v>1262.32</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>2</v>
@@ -719,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="M4" s="8">
-        <v>226.2</v>
+        <v>461.2</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>2</v>
@@ -767,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="M5" s="4">
-        <v>22.8</v>
+        <v>64.02</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>2</v>
@@ -815,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="M6" s="8">
-        <v>1292.5</v>
+        <v>1302.5</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>2</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="M7" s="4">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>2</v>
@@ -965,14 +965,14 @@
       </c>
       <c r="M9" s="10">
         <f>SUM(M3:M8)</f>
-        <v>2926.81</v>
+        <v>4276.04</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="O9" s="10">
         <f>C9+E9+G9+I9+K9+M9</f>
-        <v>31221.27</v>
+        <v>32570.5</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1047,12 +1047,12 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>195.12066666666666</v>
+        <v>285.0693333333333</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
-        <v>390.26587499999999</v>
+        <v>407.13125000000002</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1076,7 +1076,7 @@
       <c r="N14" s="11"/>
       <c r="O14" s="13">
         <f>O9</f>
-        <v>31221.27</v>
+        <v>32570.5</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       <c r="N16" s="11"/>
       <c r="O16" s="13">
         <f>O14/O15</f>
-        <v>390.26587499999999</v>
+        <v>407.13125000000002</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC42215-2C42-497A-B1AD-FABB5592682A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643C53CA-376A-425B-82FE-47092711F8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -719,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="M4" s="8">
-        <v>461.2</v>
+        <v>598.20000000000005</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>2</v>
@@ -767,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="M5" s="4">
-        <v>64.02</v>
+        <v>107.64</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>2</v>
@@ -815,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="M6" s="8">
-        <v>1302.5</v>
+        <v>1351.37</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>2</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="M7" s="4">
-        <v>586</v>
+        <v>866</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>2</v>
@@ -965,14 +965,14 @@
       </c>
       <c r="M9" s="10">
         <f>SUM(M3:M8)</f>
-        <v>4276.04</v>
+        <v>4785.53</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="O9" s="10">
         <f>C9+E9+G9+I9+K9+M9</f>
-        <v>32570.5</v>
+        <v>33079.99</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1047,12 +1047,12 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>285.0693333333333</v>
+        <v>319.03533333333331</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
-        <v>407.13125000000002</v>
+        <v>413.49987499999997</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1076,7 +1076,7 @@
       <c r="N14" s="11"/>
       <c r="O14" s="13">
         <f>O9</f>
-        <v>32570.5</v>
+        <v>33079.99</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       <c r="N16" s="11"/>
       <c r="O16" s="13">
         <f>O14/O15</f>
-        <v>407.13125000000002</v>
+        <v>413.49987499999997</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643C53CA-376A-425B-82FE-47092711F8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96925CFE-59DE-4BD8-8C68-19E4445D21C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,7 +671,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="4">
-        <v>1262.32</v>
+        <v>2267.1799999999998</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>2</v>
@@ -719,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="M4" s="8">
-        <v>598.20000000000005</v>
+        <v>1262.71</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>2</v>
@@ -767,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="M5" s="4">
-        <v>107.64</v>
+        <v>190.74</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>2</v>
@@ -815,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="M6" s="8">
-        <v>1351.37</v>
+        <v>1888.42</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>2</v>
@@ -965,14 +965,14 @@
       </c>
       <c r="M9" s="10">
         <f>SUM(M3:M8)</f>
-        <v>4785.53</v>
+        <v>7075.05</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="O9" s="10">
         <f>C9+E9+G9+I9+K9+M9</f>
-        <v>33079.99</v>
+        <v>35369.51</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1047,12 +1047,12 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>319.03533333333331</v>
+        <v>471.67</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
-        <v>413.49987499999997</v>
+        <v>442.118875</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1076,7 +1076,7 @@
       <c r="N14" s="11"/>
       <c r="O14" s="13">
         <f>O9</f>
-        <v>33079.99</v>
+        <v>35369.51</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       <c r="N16" s="11"/>
       <c r="O16" s="13">
         <f>O14/O15</f>
-        <v>413.49987499999997</v>
+        <v>442.118875</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96925CFE-59DE-4BD8-8C68-19E4445D21C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0EF9E5-E943-4D0E-8580-5E268EC14459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="M7" s="4">
-        <v>866</v>
+        <v>1346</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>2</v>
@@ -965,14 +965,14 @@
       </c>
       <c r="M9" s="10">
         <f>SUM(M3:M8)</f>
-        <v>7075.05</v>
+        <v>7555.05</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="O9" s="10">
         <f>C9+E9+G9+I9+K9+M9</f>
-        <v>35369.51</v>
+        <v>35849.51</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1047,12 +1047,12 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>471.67</v>
+        <v>503.67</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
-        <v>442.118875</v>
+        <v>448.118875</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1076,7 +1076,7 @@
       <c r="N14" s="11"/>
       <c r="O14" s="13">
         <f>O9</f>
-        <v>35369.51</v>
+        <v>35849.51</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       <c r="N16" s="11"/>
       <c r="O16" s="13">
         <f>O14/O15</f>
-        <v>442.118875</v>
+        <v>448.118875</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gesto\OneDrive\Área de Trabalho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0EF9E5-E943-4D0E-8580-5E268EC14459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B1A04E-D6B8-42B8-A381-54DF77983E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1">
         <f>C10+E10+G10+I10+K10+M10</f>
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1047,12 +1047,12 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>503.67</v>
+        <v>419.72500000000002</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
-        <v>448.118875</v>
+        <v>431.92180722891567</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1098,7 +1098,7 @@
       <c r="N15" s="11"/>
       <c r="O15" s="14">
         <f>O10</f>
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       <c r="N16" s="11"/>
       <c r="O16" s="13">
         <f>O14/O15</f>
-        <v>448.118875</v>
+        <v>431.92180722891567</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gesto\OneDrive\Área de Trabalho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B1A04E-D6B8-42B8-A381-54DF77983E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E9CD89-8FD2-4394-8451-733B5B155B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -671,7 +671,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="4">
-        <v>2267.1799999999998</v>
+        <v>2809.89</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>2</v>
@@ -719,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="M4" s="8">
-        <v>1262.71</v>
+        <v>1447.71</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>2</v>
@@ -767,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="M5" s="4">
-        <v>190.74</v>
+        <v>210.74</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>2</v>
@@ -815,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="M6" s="8">
-        <v>1888.42</v>
+        <v>2069.3200000000002</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>2</v>
@@ -965,14 +965,14 @@
       </c>
       <c r="M9" s="10">
         <f>SUM(M3:M8)</f>
-        <v>7555.05</v>
+        <v>8483.66</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="O9" s="10">
         <f>C9+E9+G9+I9+K9+M9</f>
-        <v>35849.51</v>
+        <v>36778.119999999995</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1047,12 +1047,12 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>419.72500000000002</v>
+        <v>471.31444444444446</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
-        <v>431.92180722891567</v>
+        <v>443.1098795180722</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1076,7 +1076,7 @@
       <c r="N14" s="11"/>
       <c r="O14" s="13">
         <f>O9</f>
-        <v>35849.51</v>
+        <v>36778.119999999995</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       <c r="N16" s="11"/>
       <c r="O16" s="13">
         <f>O14/O15</f>
-        <v>431.92180722891567</v>
+        <v>443.1098795180722</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E9CD89-8FD2-4394-8451-733B5B155B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598AF480-0FC2-4B79-A2C0-3942FA225E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -719,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="M4" s="8">
-        <v>1447.71</v>
+        <v>1623.41</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>2</v>
@@ -767,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="M5" s="4">
-        <v>210.74</v>
+        <v>238.74</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>2</v>
@@ -965,14 +965,14 @@
       </c>
       <c r="M9" s="10">
         <f>SUM(M3:M8)</f>
-        <v>8483.66</v>
+        <v>8687.36</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="O9" s="10">
         <f>C9+E9+G9+I9+K9+M9</f>
-        <v>36778.119999999995</v>
+        <v>36981.82</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1047,12 +1047,12 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12">
         <f>IF(M10&gt;0,M9/M10,0)</f>
-        <v>471.31444444444446</v>
+        <v>482.63111111111112</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
-        <v>443.1098795180722</v>
+        <v>445.56409638554214</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1076,7 +1076,7 @@
       <c r="N14" s="11"/>
       <c r="O14" s="13">
         <f>O9</f>
-        <v>36778.119999999995</v>
+        <v>36981.82</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
       <c r="N16" s="11"/>
       <c r="O16" s="13">
         <f>O14/O15</f>
-        <v>443.1098795180722</v>
+        <v>445.56409638554214</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598AF480-0FC2-4B79-A2C0-3942FA225E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AF624F-2910-4C94-B1FB-5DE9EE0CD048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="21">
   <si>
     <t>CONTROLE DE GASTOS</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>VIAGEM 06</t>
+  </si>
+  <si>
+    <t>VIAGEM 07</t>
   </si>
 </sst>
 </file>
@@ -547,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -563,11 +566,13 @@
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="5" customWidth="1"/>
+    <col min="14" max="14" width="3" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="5.140625" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -585,8 +590,10 @@
       <c r="M1" s="16"/>
       <c r="N1" s="16"/>
       <c r="O1" s="16"/>
-    </row>
-    <row r="2" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+    </row>
+    <row r="2" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -630,10 +637,16 @@
         <v>2</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -676,12 +689,18 @@
       <c r="N3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="4">
+        <v>200</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="5">
         <f>C3+E3+G3+I3</f>
         <v>8973.93</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -724,12 +743,18 @@
       <c r="N4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="5">
-        <f t="shared" ref="O4:O8" si="0">C4+E4+G4+I4</f>
+      <c r="O4" s="8">
+        <v>247.27</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="5">
+        <f t="shared" ref="Q4:Q8" si="0">C4+E4+G4+I4</f>
         <v>4664.8799999999992</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -772,12 +797,18 @@
       <c r="N5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="5">
         <f t="shared" si="0"/>
         <v>566.39</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -820,12 +851,18 @@
       <c r="N6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="8">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="5">
         <f t="shared" si="0"/>
         <v>985.71</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -868,12 +905,18 @@
       <c r="N7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="5">
         <f t="shared" si="0"/>
         <v>5427.79</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
@@ -916,12 +959,18 @@
       <c r="N8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="5">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
@@ -967,15 +1016,20 @@
         <f>SUM(M3:M8)</f>
         <v>8687.36</v>
       </c>
-      <c r="N9" s="9" t="s">
-        <v>2</v>
-      </c>
+      <c r="N9" s="10"/>
       <c r="O9" s="10">
+        <f>SUM(O3:O8)</f>
+        <v>480.96999999999997</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="10">
         <f>C9+E9+G9+I9+K9+M9</f>
         <v>36981.82</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -1005,11 +1059,15 @@
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1">
+        <v>5</v>
+      </c>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1">
         <f>C10+E10+G10+I10+K10+M10</f>
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -1049,15 +1107,20 @@
         <f>IF(M10&gt;0,M9/M10,0)</f>
         <v>482.63111111111112</v>
       </c>
-      <c r="N11" s="1"/>
+      <c r="N11" s="12"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
+        <v>96.193999999999988</v>
+      </c>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="12">
+        <f>IF(Q10&gt;0,Q9/Q10,0)</f>
         <v>445.56409638554214</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>6</v>
       </c>
@@ -1074,12 +1137,14 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
-      <c r="O14" s="13">
-        <f>O9</f>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="13">
+        <f>Q9</f>
         <v>36981.82</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>15</v>
       </c>
@@ -1096,12 +1161,14 @@
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
-      <c r="O15" s="14">
-        <f>O10</f>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="14">
+        <f>Q10</f>
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
@@ -1118,14 +1185,16 @@
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
-      <c r="O16" s="13">
-        <f>O14/O15</f>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="13">
+        <f>Q14/Q15</f>
         <v>445.56409638554214</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AF624F-2910-4C94-B1FB-5DE9EE0CD048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460E818A-E139-437D-9809-95C966CA2BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,7 +690,7 @@
         <v>2</v>
       </c>
       <c r="O3" s="4">
-        <v>200</v>
+        <v>510.61</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>2</v>
@@ -798,7 +798,7 @@
         <v>2</v>
       </c>
       <c r="O5" s="4">
-        <v>0</v>
+        <v>53.98</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>2</v>
@@ -852,7 +852,7 @@
         <v>2</v>
       </c>
       <c r="O6" s="8">
-        <v>33.700000000000003</v>
+        <v>539.70000000000005</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>2</v>
@@ -1019,7 +1019,7 @@
       <c r="N9" s="10"/>
       <c r="O9" s="10">
         <f>SUM(O3:O8)</f>
-        <v>480.96999999999997</v>
+        <v>1351.56</v>
       </c>
       <c r="P9" s="9" t="s">
         <v>2</v>
@@ -1110,7 +1110,7 @@
       <c r="N11" s="12"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
-        <v>96.193999999999988</v>
+        <v>270.31200000000001</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="12">

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460E818A-E139-437D-9809-95C966CA2BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB5E082-0F77-4614-93FF-943665575572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="22">
   <si>
     <t>CONTROLE DE GASTOS</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>VIAGEM 07</t>
+  </si>
+  <si>
+    <t>VIAGEM 08</t>
   </si>
 </sst>
 </file>
@@ -550,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -568,11 +571,13 @@
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="14" width="3" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="5.140625" customWidth="1"/>
+    <col min="16" max="16" width="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -592,8 +597,10 @@
       <c r="O1" s="16"/>
       <c r="P1" s="16"/>
       <c r="Q1" s="16"/>
-    </row>
-    <row r="2" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+    </row>
+    <row r="2" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -643,10 +650,16 @@
         <v>2</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -690,17 +703,23 @@
         <v>2</v>
       </c>
       <c r="O3" s="4">
-        <v>510.61</v>
+        <v>762.36</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="5">
-        <f>C3+E3+G3+I3</f>
-        <v>8973.93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q3" s="4">
+        <v>414.43</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <f>C3+E3+G3+I3+K3+M3+O3+Q3</f>
+        <v>15041.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -744,17 +763,23 @@
         <v>2</v>
       </c>
       <c r="O4" s="8">
-        <v>247.27</v>
+        <v>345.27</v>
       </c>
       <c r="P4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="Q4" s="5">
-        <f t="shared" ref="Q4:Q8" si="0">C4+E4+G4+I4</f>
-        <v>4664.8799999999992</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="8">
+        <v>53</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <f t="shared" ref="S4:S8" si="0">C4+E4+G4+I4+K4+M4+O4+Q4</f>
+        <v>7890.32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -803,12 +828,18 @@
       <c r="P5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
         <f t="shared" si="0"/>
-        <v>566.39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1089.17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -852,17 +883,23 @@
         <v>2</v>
       </c>
       <c r="O6" s="8">
-        <v>539.70000000000005</v>
+        <v>638.67999999999995</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="8">
+        <v>200</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
         <f t="shared" si="0"/>
-        <v>985.71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4325.1600000000008</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -911,12 +948,18 @@
       <c r="P7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
         <f t="shared" si="0"/>
-        <v>5427.79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8703.7900000000009</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
@@ -965,12 +1008,18 @@
       <c r="P8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="Q8" s="8">
+        <v>600</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
         <f t="shared" si="0"/>
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
@@ -1019,17 +1068,22 @@
       <c r="N9" s="10"/>
       <c r="O9" s="10">
         <f>SUM(O3:O8)</f>
-        <v>1351.56</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>2</v>
-      </c>
+        <v>1800.29</v>
+      </c>
+      <c r="P9" s="10"/>
       <c r="Q9" s="10">
+        <f>SUM(Q3:Q8)</f>
+        <v>1267.43</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="S9" s="10">
         <f>C9+E9+G9+I9+K9+M9</f>
         <v>36981.82</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -1063,11 +1117,15 @@
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1">
-        <f>C10+E10+G10+I10+K10+M10</f>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1">
+        <f>C10+E10+G10+I10+K10+M10+O10+Q10</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -1110,17 +1168,22 @@
       <c r="N11" s="12"/>
       <c r="O11" s="12">
         <f>IF(O10&gt;0,O9/O10,0)</f>
-        <v>270.31200000000001</v>
-      </c>
-      <c r="P11" s="1"/>
+        <v>360.05799999999999</v>
+      </c>
+      <c r="P11" s="12"/>
       <c r="Q11" s="12">
         <f>IF(Q10&gt;0,Q9/Q10,0)</f>
-        <v>445.56409638554214</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>84.495333333333335</v>
+      </c>
+      <c r="R11" s="1"/>
+      <c r="S11" s="12">
+        <f>IF(S10&gt;0,S9/S10,0)</f>
+        <v>359.04679611650488</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>6</v>
       </c>
@@ -1139,12 +1202,14 @@
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
-      <c r="Q14" s="13">
-        <f>Q9</f>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="13">
+        <f>S9</f>
         <v>36981.82</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>15</v>
       </c>
@@ -1163,12 +1228,14 @@
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
-      <c r="Q15" s="14">
-        <f>Q10</f>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="14">
+        <f>S10</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
@@ -1187,14 +1254,16 @@
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
-      <c r="Q16" s="13">
-        <f>Q14/Q15</f>
-        <v>445.56409638554214</v>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="13">
+        <f>S14/S15</f>
+        <v>359.04679611650488</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB5E082-0F77-4614-93FF-943665575572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907CDFB4-732E-46C7-9F3A-4516E85529EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -709,14 +709,14 @@
         <v>2</v>
       </c>
       <c r="Q3" s="4">
-        <v>414.43</v>
+        <v>1758.61</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="S3" s="5">
         <f>C3+E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>15041.1</v>
+        <v>16385.28</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -769,14 +769,14 @@
         <v>2</v>
       </c>
       <c r="Q4" s="8">
-        <v>53</v>
+        <v>323.7</v>
       </c>
       <c r="R4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" ref="S4:S8" si="0">C4+E4+G4+I4+K4+M4+O4+Q4</f>
-        <v>7890.32</v>
+        <v>8161.0199999999995</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -829,14 +829,14 @@
         <v>2</v>
       </c>
       <c r="Q5" s="4">
-        <v>0</v>
+        <v>159.85</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" si="0"/>
-        <v>1089.17</v>
+        <v>1249.02</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -889,14 +889,14 @@
         <v>2</v>
       </c>
       <c r="Q6" s="8">
-        <v>200</v>
+        <v>259.04000000000002</v>
       </c>
       <c r="R6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="0"/>
-        <v>4325.1600000000008</v>
+        <v>4384.2000000000007</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -949,14 +949,14 @@
         <v>2</v>
       </c>
       <c r="Q7" s="4">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="R7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="0"/>
-        <v>8703.7900000000009</v>
+        <v>9389.7900000000009</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1073,7 +1073,7 @@
       <c r="P9" s="10"/>
       <c r="Q9" s="10">
         <f>SUM(Q3:Q8)</f>
-        <v>1267.43</v>
+        <v>3787.2</v>
       </c>
       <c r="R9" s="9" t="s">
         <v>2</v>
@@ -1173,7 +1173,7 @@
       <c r="P11" s="12"/>
       <c r="Q11" s="12">
         <f>IF(Q10&gt;0,Q9/Q10,0)</f>
-        <v>84.495333333333335</v>
+        <v>252.48</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="12">

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907CDFB4-732E-46C7-9F3A-4516E85529EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79AEC2D-EFCA-4AC3-9B95-FC53BE312CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -709,14 +709,14 @@
         <v>2</v>
       </c>
       <c r="Q3" s="4">
-        <v>1758.61</v>
+        <v>2746.85</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="S3" s="5">
         <f>C3+E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>16385.28</v>
+        <v>17373.52</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -769,14 +769,14 @@
         <v>2</v>
       </c>
       <c r="Q4" s="8">
-        <v>323.7</v>
+        <v>978.34</v>
       </c>
       <c r="R4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" ref="S4:S8" si="0">C4+E4+G4+I4+K4+M4+O4+Q4</f>
-        <v>8161.0199999999995</v>
+        <v>8815.66</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -889,14 +889,14 @@
         <v>2</v>
       </c>
       <c r="Q6" s="8">
-        <v>259.04000000000002</v>
+        <v>364.84</v>
       </c>
       <c r="R6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="0"/>
-        <v>4384.2000000000007</v>
+        <v>4490.0000000000009</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -949,14 +949,14 @@
         <v>2</v>
       </c>
       <c r="Q7" s="4">
-        <v>686</v>
+        <v>1354</v>
       </c>
       <c r="R7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="0"/>
-        <v>9389.7900000000009</v>
+        <v>10057.790000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1073,7 +1073,7 @@
       <c r="P9" s="10"/>
       <c r="Q9" s="10">
         <f>SUM(Q3:Q8)</f>
-        <v>3787.2</v>
+        <v>6203.88</v>
       </c>
       <c r="R9" s="9" t="s">
         <v>2</v>
@@ -1173,7 +1173,7 @@
       <c r="P11" s="12"/>
       <c r="Q11" s="12">
         <f>IF(Q10&gt;0,Q9/Q10,0)</f>
-        <v>252.48</v>
+        <v>413.59199999999998</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="12">

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79AEC2D-EFCA-4AC3-9B95-FC53BE312CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E7496F-351D-445F-94D1-645896E0CCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -709,14 +709,14 @@
         <v>2</v>
       </c>
       <c r="Q3" s="4">
-        <v>2746.85</v>
+        <v>3246.94</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="S3" s="5">
         <f>C3+E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>17373.52</v>
+        <v>17873.61</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -769,14 +769,14 @@
         <v>2</v>
       </c>
       <c r="Q4" s="8">
-        <v>978.34</v>
+        <v>1040.3900000000001</v>
       </c>
       <c r="R4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" ref="S4:S8" si="0">C4+E4+G4+I4+K4+M4+O4+Q4</f>
-        <v>8815.66</v>
+        <v>8877.7099999999991</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1073,14 +1073,14 @@
       <c r="P9" s="10"/>
       <c r="Q9" s="10">
         <f>SUM(Q3:Q8)</f>
-        <v>6203.88</v>
+        <v>6766.02</v>
       </c>
       <c r="R9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="S9" s="10">
-        <f>C9+E9+G9+I9+K9+M9</f>
-        <v>36981.82</v>
+        <f>C9+E9+G9+I9+K9+M9+O9+Q9</f>
+        <v>45548.130000000005</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1">
         <f>C10+E10+G10+I10+K10+M10+O10+Q10</f>
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1173,12 +1173,12 @@
       <c r="P11" s="12"/>
       <c r="Q11" s="12">
         <f>IF(Q10&gt;0,Q9/Q10,0)</f>
-        <v>413.59199999999998</v>
+        <v>375.89000000000004</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="12">
         <f>IF(S10&gt;0,S9/S10,0)</f>
-        <v>359.04679611650488</v>
+        <v>429.69933962264156</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1206,7 +1206,7 @@
       <c r="R14" s="11"/>
       <c r="S14" s="13">
         <f>S9</f>
-        <v>36981.82</v>
+        <v>45548.130000000005</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1232,7 +1232,7 @@
       <c r="R15" s="11"/>
       <c r="S15" s="14">
         <f>S10</f>
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1258,7 +1258,7 @@
       <c r="R16" s="11"/>
       <c r="S16" s="13">
         <f>S14/S15</f>
-        <v>359.04679611650488</v>
+        <v>429.69933962264156</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E7496F-351D-445F-94D1-645896E0CCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B7FCC5-C751-4602-875F-C798130B30AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -709,14 +709,14 @@
         <v>2</v>
       </c>
       <c r="Q3" s="4">
-        <v>3246.94</v>
+        <v>3656.99</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="S3" s="5">
         <f>C3+E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>17873.61</v>
+        <v>18283.66</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -769,14 +769,14 @@
         <v>2</v>
       </c>
       <c r="Q4" s="8">
-        <v>1040.3900000000001</v>
+        <v>1357.77</v>
       </c>
       <c r="R4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" ref="S4:S8" si="0">C4+E4+G4+I4+K4+M4+O4+Q4</f>
-        <v>8877.7099999999991</v>
+        <v>9195.09</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -889,14 +889,14 @@
         <v>2</v>
       </c>
       <c r="Q6" s="8">
-        <v>364.84</v>
+        <v>605.30999999999995</v>
       </c>
       <c r="R6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="0"/>
-        <v>4490.0000000000009</v>
+        <v>4730.4700000000012</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1073,14 +1073,14 @@
       <c r="P9" s="10"/>
       <c r="Q9" s="10">
         <f>SUM(Q3:Q8)</f>
-        <v>6766.02</v>
+        <v>7733.92</v>
       </c>
       <c r="R9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="S9" s="10">
         <f>C9+E9+G9+I9+K9+M9+O9+Q9</f>
-        <v>45548.130000000005</v>
+        <v>46516.03</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1173,12 +1173,12 @@
       <c r="P11" s="12"/>
       <c r="Q11" s="12">
         <f>IF(Q10&gt;0,Q9/Q10,0)</f>
-        <v>375.89000000000004</v>
+        <v>429.66222222222223</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="12">
         <f>IF(S10&gt;0,S9/S10,0)</f>
-        <v>429.69933962264156</v>
+        <v>438.83047169811317</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1206,7 +1206,7 @@
       <c r="R14" s="11"/>
       <c r="S14" s="13">
         <f>S9</f>
-        <v>45548.130000000005</v>
+        <v>46516.03</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1258,7 +1258,7 @@
       <c r="R16" s="11"/>
       <c r="S16" s="13">
         <f>S14/S15</f>
-        <v>429.69933962264156</v>
+        <v>438.83047169811317</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B7FCC5-C751-4602-875F-C798130B30AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1437AACE-A34E-4528-88FD-B2BC405F190A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="23">
   <si>
     <t>CONTROLE DE GASTOS</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>VIAGEM 08</t>
+  </si>
+  <si>
+    <t>VIAGEM 09</t>
   </si>
 </sst>
 </file>
@@ -553,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -573,11 +576,13 @@
     <col min="15" max="15" width="13" customWidth="1"/>
     <col min="16" max="16" width="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" customWidth="1"/>
+    <col min="18" max="18" width="3" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="5.140625" customWidth="1"/>
+    <col min="21" max="21" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -599,8 +604,10 @@
       <c r="Q1" s="16"/>
       <c r="R1" s="16"/>
       <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
     </row>
-    <row r="2" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -656,10 +663,16 @@
         <v>2</v>
       </c>
       <c r="S2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -714,12 +727,18 @@
       <c r="R3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="S3" s="5">
-        <f>C3+E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>18283.66</v>
+      <c r="S3" s="4">
+        <v>3389.81</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U3" s="5">
+        <f>C3+E3+G3+I3+K3+M3+O3+Q3+S3</f>
+        <v>21673.47</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -774,12 +793,18 @@
       <c r="R4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="S4" s="5">
-        <f t="shared" ref="S4:S8" si="0">C4+E4+G4+I4+K4+M4+O4+Q4</f>
-        <v>9195.09</v>
+      <c r="S4" s="8">
+        <v>1197.6600000000001</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="U4" s="5">
+        <f t="shared" ref="U4:U8" si="0">C4+E4+G4+I4+K4+M4+O4+Q4+S4</f>
+        <v>10392.75</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -834,12 +859,18 @@
       <c r="R5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="S5" s="5">
+      <c r="S5" s="4">
+        <v>73.989999999999995</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U5" s="5">
         <f t="shared" si="0"/>
-        <v>1249.02</v>
+        <v>1323.01</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -894,12 +925,18 @@
       <c r="R6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="5">
+      <c r="S6" s="8">
+        <v>867.32</v>
+      </c>
+      <c r="T6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="U6" s="5">
         <f t="shared" si="0"/>
-        <v>4730.4700000000012</v>
+        <v>5597.7900000000009</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -954,12 +991,18 @@
       <c r="R7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="S7" s="5">
+      <c r="S7" s="4">
+        <v>1020</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U7" s="5">
         <f t="shared" si="0"/>
-        <v>10057.790000000001</v>
+        <v>11077.79</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
@@ -1014,12 +1057,18 @@
       <c r="R8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="S8" s="5">
+      <c r="S8" s="8">
+        <v>600</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="U8" s="5">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>3600</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
@@ -1075,15 +1124,20 @@
         <f>SUM(Q3:Q8)</f>
         <v>7733.92</v>
       </c>
-      <c r="R9" s="9" t="s">
-        <v>2</v>
-      </c>
+      <c r="R9" s="10"/>
       <c r="S9" s="10">
-        <f>C9+E9+G9+I9+K9+M9+O9+Q9</f>
-        <v>46516.03</v>
+        <f>SUM(S3:S8)</f>
+        <v>7148.78</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="U9" s="10">
+        <f>C9+E9+G9+I9+K9+M9+O9+Q9+S9</f>
+        <v>53664.81</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -1121,11 +1175,15 @@
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1">
-        <f>C10+E10+G10+I10+K10+M10+O10+Q10</f>
-        <v>106</v>
+        <v>15</v>
+      </c>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1">
+        <f>C10+E10+G10+I10+K10+M10+O10+Q10+S10</f>
+        <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -1175,15 +1233,20 @@
         <f>IF(Q10&gt;0,Q9/Q10,0)</f>
         <v>429.66222222222223</v>
       </c>
-      <c r="R11" s="1"/>
+      <c r="R11" s="12"/>
       <c r="S11" s="12">
         <f>IF(S10&gt;0,S9/S10,0)</f>
-        <v>438.83047169811317</v>
+        <v>476.58533333333332</v>
+      </c>
+      <c r="T11" s="1"/>
+      <c r="U11" s="12">
+        <f>IF(U10&gt;0,U9/U10,0)</f>
+        <v>443.51082644628099</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:21" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>6</v>
       </c>
@@ -1204,12 +1267,14 @@
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
-      <c r="S14" s="13">
-        <f>S9</f>
-        <v>46516.03</v>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="13">
+        <f>U9</f>
+        <v>53664.81</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>15</v>
       </c>
@@ -1230,12 +1295,14 @@
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
       <c r="R15" s="11"/>
-      <c r="S15" s="14">
-        <f>S10</f>
-        <v>106</v>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="14">
+        <f>U10</f>
+        <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
@@ -1256,14 +1323,16 @@
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
-      <c r="S16" s="13">
-        <f>S14/S15</f>
-        <v>438.83047169811317</v>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="13">
+        <f>U14/U15</f>
+        <v>443.51082644628099</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:U1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1437AACE-A34E-4528-88FD-B2BC405F190A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DB86F6-3067-49A7-A3FB-F948561D65B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,14 +728,14 @@
         <v>2</v>
       </c>
       <c r="S3" s="4">
-        <v>3389.81</v>
+        <v>3399.32</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="U3" s="5">
         <f>C3+E3+G3+I3+K3+M3+O3+Q3+S3</f>
-        <v>21673.47</v>
+        <v>21682.98</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1127,14 +1127,14 @@
       <c r="R9" s="10"/>
       <c r="S9" s="10">
         <f>SUM(S3:S8)</f>
-        <v>7148.78</v>
+        <v>7158.29</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="U9" s="10">
         <f>C9+E9+G9+I9+K9+M9+O9+Q9+S9</f>
-        <v>53664.81</v>
+        <v>53674.32</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1236,12 +1236,12 @@
       <c r="R11" s="12"/>
       <c r="S11" s="12">
         <f>IF(S10&gt;0,S9/S10,0)</f>
-        <v>476.58533333333332</v>
+        <v>477.21933333333334</v>
       </c>
       <c r="T11" s="1"/>
       <c r="U11" s="12">
         <f>IF(U10&gt;0,U9/U10,0)</f>
-        <v>443.51082644628099</v>
+        <v>443.58942148760332</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1271,7 +1271,7 @@
       <c r="T14" s="11"/>
       <c r="U14" s="13">
         <f>U9</f>
-        <v>53664.81</v>
+        <v>53674.32</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1327,7 +1327,7 @@
       <c r="T16" s="11"/>
       <c r="U16" s="13">
         <f>U14/U15</f>
-        <v>443.51082644628099</v>
+        <v>443.58942148760332</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DB86F6-3067-49A7-A3FB-F948561D65B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB1C810-9675-4E4B-9F9B-F184B085302E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,14 +728,14 @@
         <v>2</v>
       </c>
       <c r="S3" s="4">
-        <v>3399.32</v>
+        <v>2904.91</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="U3" s="5">
         <f>C3+E3+G3+I3+K3+M3+O3+Q3+S3</f>
-        <v>21682.98</v>
+        <v>21188.57</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -926,14 +926,14 @@
         <v>2</v>
       </c>
       <c r="S6" s="8">
-        <v>867.32</v>
+        <v>1007.22</v>
       </c>
       <c r="T6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="0"/>
-        <v>5597.7900000000009</v>
+        <v>5737.6900000000014</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1127,14 +1127,14 @@
       <c r="R9" s="10"/>
       <c r="S9" s="10">
         <f>SUM(S3:S8)</f>
-        <v>7158.29</v>
+        <v>6803.78</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="U9" s="10">
         <f>C9+E9+G9+I9+K9+M9+O9+Q9+S9</f>
-        <v>53674.32</v>
+        <v>53319.81</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1236,12 +1236,12 @@
       <c r="R11" s="12"/>
       <c r="S11" s="12">
         <f>IF(S10&gt;0,S9/S10,0)</f>
-        <v>477.21933333333334</v>
+        <v>453.58533333333332</v>
       </c>
       <c r="T11" s="1"/>
       <c r="U11" s="12">
         <f>IF(U10&gt;0,U9/U10,0)</f>
-        <v>443.58942148760332</v>
+        <v>440.6595867768595</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1271,7 +1271,7 @@
       <c r="T14" s="11"/>
       <c r="U14" s="13">
         <f>U9</f>
-        <v>53674.32</v>
+        <v>53319.81</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1327,7 +1327,7 @@
       <c r="T16" s="11"/>
       <c r="U16" s="13">
         <f>U14/U15</f>
-        <v>443.58942148760332</v>
+        <v>440.6595867768595</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB1C810-9675-4E4B-9F9B-F184B085302E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D739A0-5510-4A66-A6A7-726E4FF63B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,14 +728,14 @@
         <v>2</v>
       </c>
       <c r="S3" s="4">
-        <v>2904.91</v>
+        <v>3181.24</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="U3" s="5">
         <f>C3+E3+G3+I3+K3+M3+O3+Q3+S3</f>
-        <v>21188.57</v>
+        <v>21464.9</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -794,14 +794,14 @@
         <v>2</v>
       </c>
       <c r="S4" s="8">
-        <v>1197.6600000000001</v>
+        <v>1523.76</v>
       </c>
       <c r="T4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U8" si="0">C4+E4+G4+I4+K4+M4+O4+Q4+S4</f>
-        <v>10392.75</v>
+        <v>10718.85</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -926,14 +926,14 @@
         <v>2</v>
       </c>
       <c r="S6" s="8">
-        <v>1007.22</v>
+        <v>1037.21</v>
       </c>
       <c r="T6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="0"/>
-        <v>5737.6900000000014</v>
+        <v>5767.6800000000012</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1127,14 +1127,14 @@
       <c r="R9" s="10"/>
       <c r="S9" s="10">
         <f>SUM(S3:S8)</f>
-        <v>6803.78</v>
+        <v>7436.2</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="U9" s="10">
         <f>C9+E9+G9+I9+K9+M9+O9+Q9+S9</f>
-        <v>53319.81</v>
+        <v>53952.229999999996</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1">
         <f>C10+E10+G10+I10+K10+M10+O10+Q10+S10</f>
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1236,12 +1236,12 @@
       <c r="R11" s="12"/>
       <c r="S11" s="12">
         <f>IF(S10&gt;0,S9/S10,0)</f>
-        <v>453.58533333333332</v>
+        <v>437.42352941176472</v>
       </c>
       <c r="T11" s="1"/>
       <c r="U11" s="12">
         <f>IF(U10&gt;0,U9/U10,0)</f>
-        <v>440.6595867768595</v>
+        <v>438.63601626016259</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1271,7 +1271,7 @@
       <c r="T14" s="11"/>
       <c r="U14" s="13">
         <f>U9</f>
-        <v>53319.81</v>
+        <v>53952.229999999996</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1299,7 +1299,7 @@
       <c r="T15" s="11"/>
       <c r="U15" s="14">
         <f>U10</f>
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1327,7 +1327,7 @@
       <c r="T16" s="11"/>
       <c r="U16" s="13">
         <f>U14/U15</f>
-        <v>440.6595867768595</v>
+        <v>438.63601626016259</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D739A0-5510-4A66-A6A7-726E4FF63B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD07C78-A2C6-422F-87E4-771B0788F7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="24">
   <si>
     <t>CONTROLE DE GASTOS</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>VIAGEM 09</t>
+  </si>
+  <si>
+    <t>VIAGEM 10</t>
   </si>
 </sst>
 </file>
@@ -556,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -578,11 +581,13 @@
     <col min="17" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="3" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="5.140625" customWidth="1"/>
+    <col min="20" max="20" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" customWidth="1"/>
+    <col min="22" max="22" width="5.140625" customWidth="1"/>
+    <col min="23" max="23" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -606,8 +611,10 @@
       <c r="S1" s="16"/>
       <c r="T1" s="16"/>
       <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
     </row>
-    <row r="2" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -669,10 +676,16 @@
         <v>2</v>
       </c>
       <c r="U2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -733,12 +746,18 @@
       <c r="T3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="U3" s="5">
-        <f>C3+E3+G3+I3+K3+M3+O3+Q3+S3</f>
-        <v>21464.9</v>
+      <c r="U3" s="4">
+        <v>1302.67</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" s="5">
+        <f>C3+E3+G3+I3+K3+M3+O3+Q3+S3+U3</f>
+        <v>22767.57</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -799,12 +818,18 @@
       <c r="T4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="U4" s="5">
-        <f t="shared" ref="U4:U8" si="0">C4+E4+G4+I4+K4+M4+O4+Q4+S4</f>
-        <v>10718.85</v>
+      <c r="U4" s="8">
+        <v>1215.8</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="W4" s="5">
+        <f t="shared" ref="W4:W10" si="0">C4+E4+G4+I4+K4+M4+O4+Q4+S4+U4</f>
+        <v>11934.65</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -865,12 +890,18 @@
       <c r="T5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="U5" s="5">
+      <c r="U5" s="4">
+        <v>178.76</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="W5" s="5">
         <f t="shared" si="0"/>
-        <v>1323.01</v>
+        <v>1501.77</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -931,12 +962,18 @@
       <c r="T6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="U6" s="5">
+      <c r="U6" s="8">
+        <v>168.71</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="W6" s="5">
         <f t="shared" si="0"/>
-        <v>5767.6800000000012</v>
+        <v>5936.3900000000012</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -997,12 +1034,18 @@
       <c r="T7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="U7" s="5">
+      <c r="U7" s="4">
+        <v>2255</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="W7" s="5">
         <f t="shared" si="0"/>
-        <v>11077.79</v>
+        <v>13332.79</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
@@ -1063,12 +1106,18 @@
       <c r="T8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="U8" s="5">
+      <c r="U8" s="8">
+        <v>600</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="W8" s="5">
         <f t="shared" si="0"/>
-        <v>3600</v>
+        <v>4200</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
@@ -1114,17 +1163,23 @@
         <f>SUM(M3:M8)</f>
         <v>8687.36</v>
       </c>
-      <c r="N9" s="10"/>
+      <c r="N9" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="O9" s="10">
         <f>SUM(O3:O8)</f>
         <v>1800.29</v>
       </c>
-      <c r="P9" s="10"/>
+      <c r="P9" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="Q9" s="10">
         <f>SUM(Q3:Q8)</f>
         <v>7733.92</v>
       </c>
-      <c r="R9" s="10"/>
+      <c r="R9" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="S9" s="10">
         <f>SUM(S3:S8)</f>
         <v>7436.2</v>
@@ -1133,11 +1188,18 @@
         <v>2</v>
       </c>
       <c r="U9" s="10">
-        <f>C9+E9+G9+I9+K9+M9+O9+Q9+S9</f>
-        <v>53952.229999999996</v>
+        <f>SUM(U3:U8)</f>
+        <v>5720.9400000000005</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="W9" s="10">
+        <f t="shared" si="0"/>
+        <v>59673.17</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
@@ -1179,11 +1241,15 @@
       </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1">
-        <f>C10+E10+G10+I10+K10+M10+O10+Q10+S10</f>
-        <v>123</v>
+        <v>11</v>
+      </c>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1">
+        <f t="shared" si="0"/>
+        <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -1238,15 +1304,20 @@
         <f>IF(S10&gt;0,S9/S10,0)</f>
         <v>437.42352941176472</v>
       </c>
-      <c r="T11" s="1"/>
+      <c r="T11" s="12"/>
       <c r="U11" s="12">
         <f>IF(U10&gt;0,U9/U10,0)</f>
-        <v>438.63601626016259</v>
+        <v>520.08545454545458</v>
+      </c>
+      <c r="V11" s="1"/>
+      <c r="W11" s="12">
+        <f>IF(W10&gt;0,W9/W10,0)</f>
+        <v>445.32216417910445</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:21" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>6</v>
       </c>
@@ -1269,12 +1340,14 @@
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
       <c r="T14" s="11"/>
-      <c r="U14" s="13">
-        <f>U9</f>
-        <v>53952.229999999996</v>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="13">
+        <f>W9</f>
+        <v>59673.17</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>15</v>
       </c>
@@ -1297,12 +1370,14 @@
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
       <c r="T15" s="11"/>
-      <c r="U15" s="14">
-        <f>U10</f>
-        <v>123</v>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="14">
+        <f>W10</f>
+        <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
@@ -1325,14 +1400,16 @@
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
-      <c r="U16" s="13">
-        <f>U14/U15</f>
-        <v>438.63601626016259</v>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="13">
+        <f>W14/W15</f>
+        <v>445.32216417910445</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD07C78-A2C6-422F-87E4-771B0788F7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811FC662-7489-4D00-98A0-9C0C43A00E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -747,14 +747,14 @@
         <v>2</v>
       </c>
       <c r="U3" s="4">
-        <v>1302.67</v>
+        <v>2948.4</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="W3" s="5">
         <f>C3+E3+G3+I3+K3+M3+O3+Q3+S3+U3</f>
-        <v>22767.57</v>
+        <v>24413.300000000003</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -819,14 +819,14 @@
         <v>2</v>
       </c>
       <c r="U4" s="8">
-        <v>1215.8</v>
+        <v>1911.85</v>
       </c>
       <c r="V4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="W4" s="5">
         <f t="shared" ref="W4:W10" si="0">C4+E4+G4+I4+K4+M4+O4+Q4+S4+U4</f>
-        <v>11934.65</v>
+        <v>12630.7</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -891,14 +891,14 @@
         <v>2</v>
       </c>
       <c r="U5" s="4">
-        <v>178.76</v>
+        <v>225.1</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="W5" s="5">
         <f t="shared" si="0"/>
-        <v>1501.77</v>
+        <v>1548.11</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -963,14 +963,14 @@
         <v>2</v>
       </c>
       <c r="U6" s="8">
-        <v>168.71</v>
+        <v>1068.3599999999999</v>
       </c>
       <c r="V6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="W6" s="5">
         <f t="shared" si="0"/>
-        <v>5936.3900000000012</v>
+        <v>6836.0400000000009</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1107,14 +1107,14 @@
         <v>2</v>
       </c>
       <c r="U8" s="8">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="V8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="W8" s="5">
         <f t="shared" si="0"/>
-        <v>4200</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1189,14 +1189,14 @@
       </c>
       <c r="U9" s="10">
         <f>SUM(U3:U8)</f>
-        <v>5720.9400000000005</v>
+        <v>9608.7099999999991</v>
       </c>
       <c r="V9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="W9" s="10">
         <f t="shared" si="0"/>
-        <v>59673.17</v>
+        <v>63560.939999999995</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V10" s="1"/>
       <c r="W10" s="1">
         <f t="shared" si="0"/>
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1307,12 +1307,12 @@
       <c r="T11" s="12"/>
       <c r="U11" s="12">
         <f>IF(U10&gt;0,U9/U10,0)</f>
-        <v>520.08545454545458</v>
+        <v>565.21823529411756</v>
       </c>
       <c r="V11" s="1"/>
       <c r="W11" s="12">
         <f>IF(W10&gt;0,W9/W10,0)</f>
-        <v>445.32216417910445</v>
+        <v>454.00671428571422</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1344,7 +1344,7 @@
       <c r="V14" s="11"/>
       <c r="W14" s="13">
         <f>W9</f>
-        <v>59673.17</v>
+        <v>63560.939999999995</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1374,7 +1374,7 @@
       <c r="V15" s="11"/>
       <c r="W15" s="14">
         <f>W10</f>
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1404,7 +1404,7 @@
       <c r="V16" s="11"/>
       <c r="W16" s="13">
         <f>W14/W15</f>
-        <v>445.32216417910445</v>
+        <v>454.00671428571422</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811FC662-7489-4D00-98A0-9C0C43A00E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9562C9A-680D-4AB9-9EC9-410399C50747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,14 +747,14 @@
         <v>2</v>
       </c>
       <c r="U3" s="4">
-        <v>2948.4</v>
+        <v>3981.07</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="W3" s="5">
         <f>C3+E3+G3+I3+K3+M3+O3+Q3+S3+U3</f>
-        <v>24413.300000000003</v>
+        <v>25445.97</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -819,14 +819,14 @@
         <v>2</v>
       </c>
       <c r="U4" s="8">
-        <v>1911.85</v>
+        <v>2401.65</v>
       </c>
       <c r="V4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="W4" s="5">
         <f t="shared" ref="W4:W10" si="0">C4+E4+G4+I4+K4+M4+O4+Q4+S4+U4</f>
-        <v>12630.7</v>
+        <v>13120.5</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -891,14 +891,14 @@
         <v>2</v>
       </c>
       <c r="U5" s="4">
-        <v>225.1</v>
+        <v>280.45</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="W5" s="5">
         <f t="shared" si="0"/>
-        <v>1548.11</v>
+        <v>1603.46</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -963,14 +963,14 @@
         <v>2</v>
       </c>
       <c r="U6" s="8">
-        <v>1068.3599999999999</v>
+        <v>1119.81</v>
       </c>
       <c r="V6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="W6" s="5">
         <f t="shared" si="0"/>
-        <v>6836.0400000000009</v>
+        <v>6887.4900000000016</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1107,14 +1107,14 @@
         <v>2</v>
       </c>
       <c r="U8" s="8">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="V8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="W8" s="5">
         <f t="shared" si="0"/>
-        <v>4800</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1189,14 +1189,14 @@
       </c>
       <c r="U9" s="10">
         <f>SUM(U3:U8)</f>
-        <v>9608.7099999999991</v>
+        <v>11837.98</v>
       </c>
       <c r="V9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="W9" s="10">
         <f t="shared" si="0"/>
-        <v>63560.939999999995</v>
+        <v>65790.209999999992</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="V10" s="1"/>
       <c r="W10" s="1">
         <f t="shared" si="0"/>
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1307,12 +1307,12 @@
       <c r="T11" s="12"/>
       <c r="U11" s="12">
         <f>IF(U10&gt;0,U9/U10,0)</f>
-        <v>565.21823529411756</v>
+        <v>473.51919999999996</v>
       </c>
       <c r="V11" s="1"/>
       <c r="W11" s="12">
         <f>IF(W10&gt;0,W9/W10,0)</f>
-        <v>454.00671428571422</v>
+        <v>444.52844594594592</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1344,7 +1344,7 @@
       <c r="V14" s="11"/>
       <c r="W14" s="13">
         <f>W9</f>
-        <v>63560.939999999995</v>
+        <v>65790.209999999992</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1374,7 +1374,7 @@
       <c r="V15" s="11"/>
       <c r="W15" s="14">
         <f>W10</f>
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1404,7 +1404,7 @@
       <c r="V16" s="11"/>
       <c r="W16" s="13">
         <f>W14/W15</f>
-        <v>454.00671428571422</v>
+        <v>444.52844594594592</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro.xlsx
+++ b/financeiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9562C9A-680D-4AB9-9EC9-410399C50747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053ABBAB-6CEC-4D49-8669-8CA9BFCBF6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle de Gastos" sheetId="1" r:id="rId1"/>
@@ -747,14 +747,14 @@
         <v>2</v>
       </c>
       <c r="U3" s="4">
-        <v>3981.07</v>
+        <v>4281.07</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="W3" s="5">
         <f>C3+E3+G3+I3+K3+M3+O3+Q3+S3+U3</f>
-        <v>25445.97</v>
+        <v>25745.97</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -819,14 +819,14 @@
         <v>2</v>
       </c>
       <c r="U4" s="8">
-        <v>2401.65</v>
+        <v>2808.84</v>
       </c>
       <c r="V4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="W4" s="5">
         <f t="shared" ref="W4:W10" si="0">C4+E4+G4+I4+K4+M4+O4+Q4+S4+U4</f>
-        <v>13120.5</v>
+        <v>13527.69</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -963,14 +963,14 @@
         <v>2</v>
       </c>
       <c r="U6" s="8">
-        <v>1119.81</v>
+        <v>1267.01</v>
       </c>
       <c r="V6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="W6" s="5">
         <f t="shared" si="0"/>
-        <v>6887.4900000000016</v>
+        <v>7034.6900000000014</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1189,14 +1189,14 @@
       </c>
       <c r="U9" s="10">
         <f>SUM(U3:U8)</f>
-        <v>11837.98</v>
+        <v>12692.369999999999</v>
       </c>
       <c r="V9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="W9" s="10">
         <f t="shared" si="0"/>
-        <v>65790.209999999992</v>
+        <v>66644.599999999991</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V10" s="1"/>
       <c r="W10" s="1">
         <f t="shared" si="0"/>
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1307,12 +1307,12 @@
       <c r="T11" s="12"/>
       <c r="U11" s="12">
         <f>IF(U10&gt;0,U9/U10,0)</f>
-        <v>473.51919999999996</v>
+        <v>488.16807692307691</v>
       </c>
       <c r="V11" s="1"/>
       <c r="W11" s="12">
         <f>IF(W10&gt;0,W9/W10,0)</f>
-        <v>444.52844594594592</v>
+        <v>447.27919463087244</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1344,7 +1344,7 @@
       <c r="V14" s="11"/>
       <c r="W14" s="13">
         <f>W9</f>
-        <v>65790.209999999992</v>
+        <v>66644.599999999991</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1374,7 +1374,7 @@
       <c r="V15" s="11"/>
       <c r="W15" s="14">
         <f>W10</f>
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1404,7 +1404,7 @@
       <c r="V16" s="11"/>
       <c r="W16" s="13">
         <f>W14/W15</f>
-        <v>444.52844594594592</v>
+        <v>447.27919463087244</v>
       </c>
     </row>
   </sheetData>
